--- a/docs/data-collection/信用卡優惠資料整理模板-v3-2026-07-29.xlsx
+++ b/docs/data-collection/信用卡優惠資料整理模板-v3-2026-07-29.xlsx
@@ -752,7 +752,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7.25" customWidth="1" min="1" max="1"/>
@@ -956,6 +956,87 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>中國信託銀行</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ctbc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>https://www.ctbcbank.com/twrbo/zh_tw/index.html</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>中國信託銀行信用卡資料，包含 LINE Pay 卡。</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>補齊：此銀行已存在於正式站資料庫（Codex 先前直接匯入），本次僅同步回 xlsx 存檔，未變更資料庫內容。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>台北富邦銀行</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>fubon</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>https://www.fubon.com/banking/</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>台北富邦銀行信用卡資料，包含 momo 卡。</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>補齊：此銀行已存在於正式站資料庫（Codex 先前直接匯入），本次僅同步回 xlsx 存檔，未變更資料庫內容。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>星展銀行</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>dbs</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>https://www.dbs.com.tw/personal/cards/</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>星展銀行信用卡</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>補齊：此銀行已存在於正式站資料庫，本次僅同步回 xlsx 存檔，未變更資料庫內容。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -968,7 +1049,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T11"/>
+  <dimension ref="A1:T19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.8799991607666" customWidth="1" min="1" max="1"/>
@@ -1815,6 +1896,628 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>中國信託LINE Pay卡</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>ctbc-line-pay-card</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>ctbc</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>https://www.ctbcbank.com/content/dam/minisite/long/creditcard/LINEPay/index.html</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>國內外一般消費1%，國外實體最高2.8%無上限，2026/07海外登錄最高5%</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>中國信託LINE Pay卡2026/7/1-12/31國內外一般消費享LINE POINTS 1%，國外實體商店消費最高2.8%（含一般1%+國外實體加碼1.8%）。2026/7/1-9/30海外實體消費需登錄可享最高5%；新戶首刷滿888元享LINE POINTS 300點。</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>常用LINE POINTS、海外實體消費或想用一卡通搭大眾運輸累點者。</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>所持LINE Pay聯名卡成功綁定LINE Pay，2026/1/1-12/31享免年費禮遇。</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>#FBF0CE</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>#F4E3AE</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>#6B5A3A</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>#6B4A32</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>#4A3222</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>國內外一般消費1%
+國外實體商店最高2.8%無上限
+2026/7/1-9/30海外實體登錄最高5%
+一卡通搭乘大眾運輸享1%</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>分期交易無LINE POINTS回饋
+海外實體5%須登錄且每週二限量
+國外實體加碼不含網路交易、條碼支付或第三方支付，依中信與國際組織認定</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>補齊：此卡已存在於正式站資料庫，本次僅同步回 xlsx 存檔，未變更資料庫內容。對應優惠（4筆，含多層回饋結構）因 xlsx 僅能表達單層回饋、重新匯入會把資料庫既有多層 RewardTier 降級成單層，故不放進 offers 工作表重新匯入，僅記錄於此備註與 CURRENT_STATE 文件。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>台北富邦momo卡</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>fubon-momo-card</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>fubon</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>https://www.fubon.com/banking/personal/credit_card/all_card/momo/momo.htm?fromUrl=web1206</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>momo通路最高3%mo幣，店外一般與海外1%現金回饋無上限</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>台北富邦momo卡2026/4/1-12/31在momo通路消費最高3%mo幣回饋，店外一般消費與海外消費享1%現金回饋無上限。2026/7/1-12/31新戶申辦momo卡，核卡後30天內完成店內1筆與店外1筆一般消費，享700 mo幣與免運券；核卡後90天內店內外一般消費再加碼2%，上限300 mo幣。</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>常在momo購物、電視購物、mo店+或跨境電商消費者。</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>#FAFAFA</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>#EBEBEB</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>#DD0C57</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>#E5E7EB</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>#9CA3AF</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>momo通路最高3%mo幣
+店外一般與海外1%現金回饋無上限
+2026下半年新戶最高1,000 mo幣與免運券
+店外回饋改為現金回饋，帳單折抵更彈性</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>momo通路回饋每期帳單上限1,000 mo幣
+新戶禮須核卡後30天內登錄並完成指定消費
+特殊商品、分期認列與回饋時間依富邦公告</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>補齊：此卡已存在於正式站資料庫，本次僅同步回 xlsx 存檔，未變更資料庫內容。對應優惠不重新匯入，理由同上。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>滙豐現金回饋御璽卡</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>hsbc-cashback-signature</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>hsbc</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>https://www.hsbc.com.tw/credit-cards/products/cashback-signature/</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>國內1.22%、海外2.22%現金回饋無上限，回饋不歸零</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>滙豐現金回饋御璽卡新年度活動辦法公告維持國內1.22%、海外2.22%現金積點回饋，現金回饋無上限、無最低消費門檻、回饋終身有效。2026/7/1-9/30仍適用新年度活動辦法。</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>不想切換方案、不想追登錄，希望用簡單無上限現金回饋作為低維護主力卡者。</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Visa御璽卡</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>#565452</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>#2C2A29</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>#F7F8FA</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>#E5E7EB</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>#9CA3AF</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>國內1.22%現金回饋
+海外2.22%現金回饋
+回饋無上限、無最低消費門檻
+現金積點終身有效</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>海外回饋排除歐盟及英國實體通路
+消費定義、除外交易與活動期間依滙豐公告
+本卡不是追求高加碼上限，而是低維護與無上限</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>補齊：此卡已存在於正式站資料庫，本次僅同步回 xlsx 存檔，未變更資料庫內容。對應優惠不重新匯入，理由同上。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>星展eco永續卡</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>dbs-eco-card</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>dbs</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>https://www.dbs.com.tw/personal-zh/cards/landing/layout.html?pid=tw-pweb-personal-zh-cards-dbs_ipass-pxmart2</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>一般消費1%無上限，指定海外實體最高5%、eco通路最高10%</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>星展eco永續卡2026/1/1-12/31國內、國外一般消費、保費與超商街口支付享1%現金積點無上限；日、韓、泰、星、美、歐於當地實體商店持卡或Apple Pay/Samsung Pay消費最高5%；Tesla充電資費、Gogoro電池資費與星展支持社會企業及中小企業等指定eco通路最高10%。2026/7/1-8/31新戶另有首刷好禮二選一。</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>重視一般消費無上限、海外實體旅遊消費，或有Tesla/Gogoro等eco通路支出的使用者。</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>#2E8049</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>#123D1F</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>#F7F8FA</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>#E5E7EB</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>#9CA3AF</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>國內外一般消費1%無上限
+指定海外實體最高5%
+指定eco通路最高10%
+保費與超商街口支付也列一般1%回饋</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>海外5%與eco 10%依指定國家、指定通路、支付方式與上限規則認定
+新戶首刷好禮限2026/7/1-8/31
+回饋排除項目與現金積點使用依星展公告</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>補齊：此卡已存在於正式站資料庫，本次僅同步回 xlsx 存檔，未變更資料庫內容。對應優惠不重新匯入，理由同上。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>中國信託uniopen聯名卡</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ctbc-uniopen-card</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>ctbc</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>https://www.ctbcbank.com/twrbo/zh_tw/cc_index/cc_product/cc_introduction_index/C_uniopen.html</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>統一企業集團與海外消費最高11% OPENPOINT回饋，綁定icash Pay可疊加回饋</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>中國信託uniopen聯名卡分為世界卡與鈦金卡，回饋以OPENPOINT點數發放。國內一般消費1%無上限；統一企業集團消費基本加碼2%，完成不同品牌踩點任務最高再加碼4%；國外一般消費2%，國外實體商店再加碼8%，依活動規則最高可達11%。綁定icash Pay於指定商店單筆滿NT$199，可再享4%加碼，另有指定品牌週期優惠。核卡後須登入中國信託銀行App連結uniopen會員，才能累積與接收OPENPOINT。</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>常在7-ELEVEN、康是美、星巴克、博客來、統一時代百貨等統一企業集團品牌消費，或有海外實體消費，且願意完成會員連結與行動支付綁定者。</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>世界卡：115/12/31前申辦首年免年費；次年年費計算期間新增消費達NT$360,000享次年免年費。鈦金卡：115/12/31前申辦首年免年費；申請中國信託電子／行動帳單或設定中國信託帳戶自動扣繳卡費享次年免年費。</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>依卡別與申辦期間適用首年免年費及次年免年費條件；實際年費以中國信託最新公告為準。</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>世界卡／鈦金卡</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Mastercard</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>國內一般消費1% OPENPOINT無上限
+統一企業集團消費基本加碼2%，完成踩點任務最高再加碼4%
+國外一般消費2%，國外實體商店再加碼8%
+綁定icash Pay指定商店單筆滿NT$199可再加碼4%</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>核卡後須在中國信託銀行App連結uniopen會員
+踩點任務需每月於不同統一企業集團品牌單筆滿NT$199
+部分活動需領券或登錄，且各項加碼有每月點數上限與名額限制
+世界卡與鈦金卡申請資格、年費條件不同</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>官方資料查證：2026-07-28；回饋與優惠以中國信託、icash Pay最新公告為準。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>中國信託中華航空聯名卡鼎尊無限卡</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>ctbc-china-airlines-infinite-card</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>ctbc</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>https://www.ctbcbank.com/twrbo/zh_tw/cc_index/cc_product/cc_introduction_index/C_CAL.html</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>鼎尊無限卡一般消費每NT$18累積1哩，生日月海外實體消費最優NT$6累積1哩</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>中國信託中華航空聯名卡鼎尊無限卡適合高頻搭乘中華航空或華信航空、重視哩程與機場禮遇的持卡人。一般消費每NT$18累積1哩；國外實體商店、華航／華信官網機票、華航eMall、華航Sky Boutique、機上免稅品及指定訂房平台等指定通路享加碼哩程，生日當月國外實體商店最優NT$6累積1哩。</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>每年搭乘華航或華信航空多次，願意負擔高年費並使用機場接送、貴賓室與華夏金卡會籍禮遇者。</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>正卡NT$22,000；附卡免年費。</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>無一般免年費條件；續卡哩活動需繳交續卡年費。</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>一般消費每NT$18=1哩
+指定通路加碼2倍哩程
+生日月海外實體消費加碼3倍，最優NT$6=1哩
+首次申辦綁定華夏會員且首刷可享華夏金卡會籍2年</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>年費高；加碼哩程有每月上限
+海外實體須為面對面交易，網路交易、條碼支付與第三方支付不列入
+部分禮遇與會員資格需申請、綁定或符合首刷條件</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>官方資料查證：2026-07-28；年費與回饋依中信最新公告為準。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>中國信託中華航空聯名卡璀璨無限卡</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>ctbc-china-airlines-signature-card</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>ctbc</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>https://www.ctbcbank.com/twrbo/zh_tw/cc_index/cc_product/cc_introduction_index/C_CAL.html</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>璀璨無限卡一般消費每NT$20累積1哩，生日月海外實體消費最優NT$6.67累積1哩</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>中國信託中華航空聯名卡璀璨無限卡提供中高階哩程累積與華航機場禮遇。一般消費每NT$20累積1哩；指定通路享加碼哩程，生日當月海外實體商店可享3倍哩程。首次申辦綁定華夏會員且完成首刷，可享華夏金卡會籍1年。</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>每年有數次華航或華信航空旅程，想兼顧哩程、貴賓室與華夏會員禮遇，但不需要鼎尊無限卡最高等級服務者。</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>正卡NT$8,000；附卡免年費。</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>無一般免年費條件；續卡哩活動需繳交續卡年費。</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>一般消費每NT$20=1哩
+指定通路加碼2倍哩程
+生日月海外實體消費加碼3倍
+首次申辦綁定華夏會員且首刷可享華夏金卡會籍1年</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>加碼哩程有每月上限
+海外實體須為面對面交易，網路交易、條碼支付與第三方支付不列入
+華夏金卡會籍與機場禮遇依活動條件辦理</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>官方資料查證：2026-07-28；年費與回饋依中信最新公告為準。</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>中國信託中華航空聯名卡商務御璽卡</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>ctbc-china-airlines-business-signature-card</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>ctbc</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>https://www.ctbcbank.com/twrbo/zh_tw/cc_index/cc_product/cc_introduction_index/C_CAL.html</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>商務御璽卡一般消費每NT$30累積1哩，首年免年費且年消費滿NT$60,000享次年免年費</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>中國信託中華航空聯名卡商務御璽卡以較低持有成本累積華航哩程。一般消費每NT$30累積1哩；國外實體商店、華航／華信官網機票、華航eMall、華航Sky Boutique及機上免稅品等指定通路享加碼哩程，生日當月海外實體商店享3倍哩程。</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>想累積華航哩程、主要使用一般消費，且希望年消費達門檻即可免次年年費的持卡人。</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>首年免年費；正卡NT$1,800；附卡NT$900。</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>年消費滿NT$60,000享次年免年費。</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>一般消費每NT$30=1哩
+指定通路加碼2倍哩程
+生日月海外實體消費加碼3倍
+首年免年費，年消費滿NT$60,000免次年年費</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>商務御璽卡不提供華夏金卡會籍升等
+加碼哩程有每月上限
+海外實體須為面對面交易，網路交易、條碼支付與第三方支付不列入</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>官方資料查證：2026-07-28；年費與回饋依中信最新公告為準。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1827,7 +2530,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S17"/>
+  <dimension ref="A1:T37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26.75" customWidth="1" min="1" max="1"/>
@@ -1849,6 +2552,7 @@
     <col width="9.75" customWidth="1" min="17" max="17"/>
     <col width="41.38000106811523" customWidth="1" min="18" max="18"/>
     <col width="26" customWidth="1" min="19" max="19"/>
+    <col width="26" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1" ht="26.39999961853027" customHeight="1">
@@ -1945,6 +2649,11 @@
       <c r="S1" s="6" t="inlineStr">
         <is>
           <t>備註</t>
+        </is>
+      </c>
+      <c r="T1" s="6" t="inlineStr">
+        <is>
+          <t>回饋層級名稱</t>
         </is>
       </c>
     </row>
@@ -3449,6 +4158,1832 @@
       <c r="S17" t="inlineStr">
         <is>
           <t>官方活動頁與台新學雜費活動頁交叉查證；水／電等費用與學雜費均有台新官方頁明載。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>中國信託LINE Pay卡回饋計畫最高16%</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>ctbc-linepay-rewards-2026h2</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>cashback</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026下半年刷中國信託LINE Pay卡，國內外一般消費1%、國外實體信用卡最高2.8%，指定商家加碼最高16%。</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>想把日常、海外與指定商家消費累積為 LINE POINTS 的 LINE Pay 使用者。</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>國內外一般消費1%</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>指定商家加碼最高16%</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>活動期間 2026/7/1-2026/12/31。使用中國信託LINE Pay卡或以 LINE Pay 綁定該卡支付，並於刷卡前完成 LINE Pay 帳號綁定，可累積 LINE POINTS。國內外一般消費享1%；信用卡於國外實體商店面對面交易最高2.8%；指定餐飲、網購、旅遊、生活等合作商家依各活動頁公告加碼，最高16%。</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>2026-12-29</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>點數回饋</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>1%</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>無上限；點數依消費金額四捨五入入點。</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>以中國信託LINE Pay卡結帳，或 LINE Pay 綁定中國信託LINE Pay卡支付。</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>需於刷卡消費前完成 LINE Pay 帳號綁定。分期交易不回饋 LINE POINTS；信用卡年費、利息、預借現金、基金、學費、稅款、公用事業費、政府規費、便利商店、全聯/大全聯、電信費、部分歐洲地區實體商店等官方列示項目不列入回饋。</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>https://www.ctbcbank.com/content/dam/minisite/long/creditcard/LINEPay/index.html</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>中信,中國信託,LINE Pay,LINE POINTS,海外消費,一般消費,指定商家</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>補齊：正式站既有資料（多層回饋，3層），本次依 v7 多層寫法重新寫回 xlsx 存檔，未變更資料庫內容。</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>國內外一般消費</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>ctbc-linepay-rewards-2026h2</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>點數回饋</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>最高2.8%</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>無上限；含一般消費1%與國外實體商店加碼1.8%。</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>限信用卡於國外實體商店面對面交易，含實體卡與 Apple Pay／Google Pay／Samsung Pay。</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>網路交易、條碼支付、第三方支付不列入國外實體商店加碼；是否符合以中國信託及國際組織系統資料為準。需於刷卡消費前完成 LINE Pay 帳號綁定。分期交易不回饋 LINE POINTS；其餘不回饋項目同上。</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>國外實體商店</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>ctbc-linepay-rewards-2026h2</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>點數回饋</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>最高16%</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>各商家活動期間、登錄名額與回饋上限不同，依官網各活動頁為準。</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>需符合指定商家、指定卡別、指定消費日、滿額或登錄等條件。</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>部分商店位於百貨、商場、機場、車站、飯店或旅館時，可能因帳單明細不同而無法認列加碼。</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>指定商家加碼</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>中國信託LINE Pay卡海外實體消費周周登最高5%</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>ctbc-linepay-overseas-physical-weekly-2026q3</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>travel</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2026/7/1-9/30 持中國信託LINE Pay信用卡至國外實體商店消費，登錄後最高享 LINE POINTS 5%。</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>2026第三季有海外實體商店消費，且願意每週二搶登錄名額的 LINE Pay卡信用卡持卡人。</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>海外實體最高5%</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>每週二3,000名登錄名額</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>活動期間 2026/7/1-2026/9/30。持中國信託LINE Pay信用卡至國外實體商店消費，活動登錄後享 LINE POINTS 最高5%，包含國外實體一般消費2.8%與2.2%加碼回饋。每週二開放3,000名登錄名額。</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>點數回饋</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>最高5%</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>每週二開放3,000名登錄名額；實際仍以中國信託活動登錄頁公告為準。</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>須持中國信託LINE Pay信用卡於國外實體商店消費並完成活動登錄。</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>LINE Pay簽帳金融卡不適用此活動。國外實體交易認定與不回饋項目依中國信託官網與活動登錄頁公告為準。</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>https://www.ctbcbank.com/content/dam/minisite/long/creditcard/LINEPay/index.html</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>中信,LINE Pay,海外,實體商店,周周登,LINE POINTS</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>補齊：正式站既有資料，本次僅同步回 xlsx 存檔，未變更資料庫內容。</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>海外實體周周登</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>中國信託LINE Pay卡新戶首刷禮最高300點</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>ctbc-linepay-new-card-gift-2026h2</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>cashback</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026/7/1-12/31 申辦 LINE Pay 卡，核卡日起30日內累積消費滿NT$888，新戶享300點、新卡享100點 LINE POINTS。</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>首次申辦中國信託信用卡或首次申辦 LINE Pay 信用卡正卡，且可在核卡後30日內刷滿NT$888者。</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>新戶300點</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>新卡100點</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>活動期間 2026/7/1-2026/12/31 前申辦中國信託LINE Pay卡，且核准日須於 2027/1/15 前。核卡日起30日內以該新卡累積消費滿NT$888，可依資格領取新戶禮 LINE POINTS 300點，或新卡禮 LINE POINTS 100點。</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>點數回饋</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>新戶300點；新卡100點</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>新戶禮與新卡禮不可同時享有；每戶正卡限領乙次。</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>核卡日起30日內以該新卡累積消費滿NT$888。</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>新戶指申辦前12個月內未持有任何中國信託信用卡正卡；新卡指首次申辦LINE Pay信用卡正卡。須於刷卡前完成LINE Pay帳號綁定；點數將於符合資格之次次月起回饋至LINE Pay卡正卡綁定之LINE Pay帳號。</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>https://www.ctbcbank.com/content/dam/minisite/long/creditcard/LINEPay/gifts.html</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>中信,LINE Pay,新戶禮,首刷禮,LINE POINTS,新卡禮</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>補齊：正式站既有資料，本次僅同步回 xlsx 存檔，未變更資料庫內容。</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>新戶禮／新卡禮</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>中國信託LINE Pay卡一卡通大眾交通1%回饋</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>ctbc-linepay-ipass-transit-2026</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>transport</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2026/1/1-12/31 使用已綁定的LINE Pay卡一卡通儲值金支付全臺大眾交通工具，高鐵與計程車除外，享LINE POINTS 1%。</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>以一卡通搭捷運、輕軌、台鐵、公車客運、公共自行車或渡輪，並已綁定LINE Pay卡者。</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>交通1%</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>回饋無上限</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>活動期間 2026/1/1-2026/12/31。持已綁定之中國信託LINE Pay信用卡或簽帳金融卡的一卡通功能，使用一卡通儲值金支付全臺大眾交通工具費用，可享 LINE POINTS 1%回饋。適用交通包含捷運輕軌、台鐵、公車客運、公共自行車、渡輪；高鐵與計程車除外。</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>點數回饋</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>1%</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>回饋無上限；正附卡分開計算，信用卡與簽帳金融卡分開計算。每月：活動期間內當月份累積消費每滿NT$100，可獲得LINE POINT 1點。</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>須使用已綁定LINE Pay卡之一卡通功能支付全臺大眾交通工具，不含高鐵、計程車；也不包含以其他行動支付方之一卡通交易。消費明細依通路資料回傳時間為準。</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>https://www.ctbcbank.com/content/dam/minisite/long/creditcard/LINEPay/index.html</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>中信,LINE Pay,一卡通,大眾交通,交通,捷運,台鐵,公車,LINE POINTS</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>補齊：正式站既有資料，本次僅同步回 xlsx 存檔，未變更資料庫內容。</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>一卡通大眾交通</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Richart卡7大方案最高3.8%</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>taishin-richart-category-rewards-2026h2</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>cashback</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>完成台新帳戶自扣後，Richart卡指定通路最高3.8%台新Point回饋。</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>日常消費通路多元、願意用Richart Life切換方案的使用者.</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>最高3.8%</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>7大方案</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>活動期間：2026/7/1-2027/3/31。
+持台新Richart卡並透過Richart Life APP切換指定方案，成功設定台新帳戶扣繳台新信用卡帳款後，於次期信用卡帳單結帳後次營業日起，指定通路最高享3.8%台新Point（信用卡）回饋；未完成設定者，切換刷加碼通路最高1.3%。一般消費另享0.3%回饋無上限。
+2026/7/8-9/30另有新上市7+1刷最高10%活動，實際通路、上限與領券規則依台新官網與Richart Life APP公告。</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>2027-03-31</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>點數回饋</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>指定通路最高3.8%；一般消費0.3%</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>各方案、領券與加碼活動依台新公告設定上限；一般消費0.3%無上限。</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>需透過Richart Life APP切換方案；成功設定台新帳戶自扣後才可升級指定通路最高3.8%。切換方案每日限一次，指定通路、支付方式、保費與不回饋交易依台新公告認定。</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>https://www.taishinbank.com.tw/TSB/personal/credit/intro/overview/cg047/?from=index</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>點數回饋,指定通路,行動支付,期間限定,保費</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>補齊：正式站既有資料，本次僅同步回 xlsx 存檔，未變更資料庫內容。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>DAWHO新戶行動支付最高20%</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>dawho-mobile-payment-new-card-2026h2</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>cashback</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>新戶申辦DAWHO卡，核卡後30日內綁指定行動支付一般消費最高20%。</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>新辦永豐卡且常用LINE Pay、Apple Pay、Google Pay、Samsung Pay或全支付者。</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>新戶最高20%</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>上限500元</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>活動期間：2026/7/1-2026/12/31。
+新戶申辦DAWHO現金回饋信用卡，於核卡後30日內一般消費綁定LINE Pay、Apple Pay、Google Pay、Samsung Pay、全支付、55688 APP或Mitsui Shopping Park Pay支付，可享最高20%刷卡金回饋，回饋上限500元。
+本活動限2026/7/1-12/31申請進件，並於2027/1/15前核卡者參加，總限量10,000戶，額滿提前終止。</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>現金回饋</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>指定行動支付最高20%刷卡金</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>回饋上限500元；總限量10,000戶。</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>核卡後30日內指定行動支付一般消費</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>限新戶；指定行動支付交易須帳單明細有明確支付名稱，且最晚須於核卡60日內請款。一般消費定義、排除項目、回饋時間依永豐公告。</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>https://bank.sinopac.com/sinopacBT/personal/credit-card/introduction/bankcard/DAWHO.html?act=ACT211214009&amp;hpp=ACT211214009</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>現金回饋,新戶,行動支付,期間限定,需登錄</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>補齊：正式站既有資料，本次僅同步回 xlsx 存檔，未變更資料庫內容。</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>中信LINE Pay海外實體最高5%</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>ctbc-linepay-overseas-physical-2026q3</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>travel</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2026/7/1-9/30國外實體消費登錄後最高5% LINE POINTS。</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>暑期出國、海外實體刷卡或Apple Pay/Google Pay/Samsung Pay消費者。</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>海外最高5%</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>一般1%</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>活動期間：2026/7/1-2026/9/30。
+持中國信託LINE Pay信用卡至國外實體商店消費，登錄後享LINE POINTS最高5%，含國外一般消費2.8%與2.2%加碼回饋。國內外一般消費2026/7/1-12/31享1%，國外實體商店消費最高2.8%無上限。
+一卡通儲值金支付全臺大眾交通工具（高鐵除外）享LINE POINTS 1%。</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>點數回饋</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>海外實體最高5%；國外實體一般最高2.8%；國內外一般1%</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>海外實體5%加碼每週二開放3,000名登錄名額；一般與國外實體基本回饋依官方規則。</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>需登錄；國外實體商店須為面對面交易，網路交易、條碼支付或第三方支付不列入。分期交易無LINE POINTS回饋，本行不回饋項目依官方公告排除。</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>https://www.ctbcbank.com/content/dam/minisite/long/creditcard/LINEPay/index.html</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>點數回饋,海外,旅遊交通,需登錄,期間限定,交通通勤</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>補齊：正式站既有資料，本次僅同步回 xlsx 存檔，未變更資料庫內容。</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>富邦momo卡店內最高3%</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>fubon-momo-shopping-2026h2</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>online-shopping</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>momo通路最高3%mo幣，店外一般與海外1%現金回饋無上限。</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>momo購物網、電視購物、mo店+與跨境電商重度使用者。</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>momo最高3%</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>新戶最高1,000</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>活動期間：2026/4/1-2026/12/31。
+持台北富邦momo卡於momo通路消費最高3% mo幣回饋；店外一般消費與海外消費享1%現金回饋無上限。momo通路包含購物網、電視購物、型錄、mo店+與跨境電商。
+2026/7/1-12/31新戶申辦momo卡正卡，核卡後30天內完成momo店內1筆與店外1筆一般消費，享700 mo幣與mo店+免運券；核卡後90天內店內與店外一般消費再享2%加碼，上限300 mo幣。</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>現金回饋</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>momo通路最高3% mo幣；店外與海外1%現金回饋；新戶加碼最高1,000 mo幣</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>momo通路每期帳單回饋上限1,000 mo幣；新戶加碼上限300 mo幣。</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>新戶首刷禮須核卡後30天內完成momo店內1筆與店外1筆一般消費。</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>新戶活動須於核卡後30天內登錄。特殊商品依商品頁標示，分期交易、回饋時間、帳號綁定與不適用項目依富邦公告。</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>https://www.fubon.com/banking/personal/credit_card/all_card/momo/momo.htm?fromUrl=web1206</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>現金回饋,網購電商,新戶,期間限定,指定通路</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>補齊：正式站既有資料，本次僅同步回 xlsx 存檔，未變更資料庫內容。</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>滙豐現金回饋國內1.22%</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>hsbc-cashback-signature-2026q3</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>cashback</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>現金回饋御璽卡國內1.22%、海外2.22%，無上限且回饋不歸零。</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>不想切換方案或登錄，想要低維護現金回饋者。</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>國內1.22%</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>海外2.22%</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>活動期間：2026/7/1-2026/9/30。
+滙豐現金回饋御璽卡新年度活動辦法公告維持不變，國內一般新增消費享現金積點1.22%，海外一般新增消費享2.22%。現金回饋無上限、無最低消費門檻，且回饋終身有效。</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>現金回饋</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>國內1.22%；海外2.22%</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>無上限。</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>海外2.22%不含歐盟及英國實體通路。合格消費、除外項目、活動辦法與後續延長期間依滙豐官方公告。</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>https://www.hsbc.com.tw/credit-cards/products/cashback-signature/</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>現金回饋,免切換,海外,長期權益</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>補齊：正式站既有資料，本次僅同步回 xlsx 存檔，未變更資料庫內容。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>星展eco永續卡eco最高10%</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>dbs-eco-card-rewards-2026</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>cashback</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>一般消費1%無上限，指定海外實體最高5%、eco通路最高10%。</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>有海外實體、保費、超商街口支付、Tesla或Gogoro充電資費支出者。</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>一般1%無上限</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>eco最高10%</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>活動期間：2026/1/1-2026/12/31。
+星展eco永續卡國內／國外一般消費、保費與超商街口支付享1%現金積點回饋無上限。於日本、韓國、泰國、新加坡、美國、歐洲持卡或以Apple Pay／Samsung Pay於當地實體商店一般消費，享最高5%回饋；Tesla充電資費、Gogoro電池資費、星展支持的社會企業與中小企業等指定eco通路最高10%。
+2026/7/1-8/31新戶申辦另有首刷及指定任務好禮二選一。</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>現金回饋</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>一般消費1%；指定海外實體最高5%；指定eco通路最高10%</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>指定海外與eco通路加碼上限依星展官方權益規則。</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>最高5%與10%須符合指定國家、指定通路、支付方式與一般消費定義。回饋排除項目、現金積點規則與新戶首刷條件依星展公告。</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>https://www.dbs.com.tw/personal-zh/cards/landing/layout.html?pid=tw-pweb-personal-zh-cards-dbs_ipass-pxmart2</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>現金回饋,海外,保費,加油,交通通勤,期間限定</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>補齊：正式站既有資料，本次僅同步回 xlsx 存檔，未變更資料庫內容。</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>中國信託uniopen聯名卡消費回饋最高11%</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>ctbc-uniopen-core-rewards-2026h2</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>cashback</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2026/7/1至8/31，國內一般消費1%，統一企業集團與海外消費依任務最高11% OPENPOINT。</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>統一企業集團品牌或海外實體消費比例高，並可完成uniopen會員連結與指定任務的持卡人。</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>國內一般消費1%無上限；統一企業集團基本加碼2%（每月上限500點）</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>不同統一企業集團品牌消費2至5家以上，踩點任務最高加碼4%（每月上限500點）</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>活動期間2026-07-01至2026-08-31。持中國信託uniopen聯名卡並於中信App連結uniopen會員：國內一般消費享1% OPENPOINT無上限；統一企業集團消費基本加碼2%，每月於不同品牌單筆消費滿NT$199，消費2家加碼1%、3家加碼2%、4家加碼3%、5家以上加碼4%；國外一般消費2%，國外實體商店依活動再加碼，整體最高可達11%。</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>點數回饋</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>最高11% OPENPOINT</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>統一企業集團基本加碼每戶每月500點；踩點任務每戶每月500點；海外實體加碼每戶每月500點。</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>統一企業集團踩點每個不同品牌單筆滿NT$199。</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>需核卡後登入中國信託銀行App連結uniopen會員；踩點須使用不同品牌；正附卡歸戶及回饋計算依銀行規則；不適用交易與實際認列通路依中國信託公告。卡優文章與icash Pay公告為交叉整理，官方規則優先。</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>https://www.ctbcbank.com/twrbo/zh_tw/cc_index/cc_product/cc_introduction_index/C_uniopen.html</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>點數回饋,指定通路,加碼,海外,期間限定,統一企業集團</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>交叉來源：https://www.cardu.com.tw/message/detail.php?63682；https://www.icashpay.com.tw/advertMessage/view/id/2370。</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>中國信託uniopen聯名卡綁定icash Pay單筆滿199加碼4%</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>ctbc-uniopen-icashpay-stack-2026q3</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>cashback</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2026/7/1至8/31，綁定icash Pay於指定商店單筆滿NT$199，享4% OPENPOINT加碼。</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>平常使用icash Pay消費，且能完成綁卡與指定商店單筆門檻的uniopen持卡人。</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>icash Pay指定商店單筆滿NT$199加碼4%</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>可與uniopen統一企業集團踩點任務疊加，最高整理至7%或依品牌活動規則計算</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>活動期間2026-07-01至2026-08-31。以icash Pay綁定中國信託uniopen聯名卡，於指定商店單筆消費滿NT$199（含）享OPENPOINT加碼4%。每一icash Pay會員每月回饋上限150點，每月總回饋上限300萬點；可與uniopen聯名卡一般消費及統一企業集團踩點回饋疊加。icash Pay另有自動加值活動，需另行登錄，不能直接視為信用卡固有回饋。</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>點數回饋</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>加碼4% OPENPOINT</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>每一icash Pay會員每月150點；每月總回饋上限300萬點。</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>指定商店單筆滿NT$199。</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>需先將uniopen聯名卡綁定icash Pay；交易須符合指定商店與活動認列；icash Pay自動加值10%為另行登錄活動，適用卡版與活動條件依icash Pay公告。</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>https://www.icashpay.com.tw/advertMessage/view/id/2370</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>行動支付,點數回饋,加碼,指定通路,期間限定</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>交叉來源：https://www.ctbcbank.com/twrbo/zh_tw/cc_index/cc_product/cc_introduction_index/C_uniopen.html；https://www.cardu.com.tw/message/detail.php?63682。</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>中國信託uniopen聯名卡海外實體消費最高11%</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>ctbc-uniopen-overseas-physical-2026h2</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>travel</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2026/7/1至8/31，海外一般消費2%，海外實體商店再加碼，最高11% OPENPOINT。</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>有海外實體刷卡需求，並能接受每月加碼點數上限的uniopen持卡人。</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>海外一般消費2% OPENPOINT無上限</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>海外實體商店再加碼8%，整理後最高11%</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>活動期間2026-07-01至2026-08-31。持中國信託uniopen聯名卡於海外實體商店消費，享海外一般消費回饋，符合活動認列者再享海外實體商店加碼，整體最高11% OPENPOINT。海外實體加碼每戶每月上限500點；超過上限後仍依一般海外消費規則回饋。海外交易可能另有國外交易服務費，實際認列國家、商店型態、排除交易與回饋入點時間以中國信託公告為準。</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>點數回饋</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>最高11% OPENPOINT</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>海外實體商店加碼每戶每月500點；海外一般消費回饋無上限。</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>海外實體商店刷卡消費。</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>須完成uniopen會員連結；僅限銀行認列的海外實體商店交易；海外網路交易與不適用交易依官方規則辦理；實際回饋可能抵銷部分海外交易服務費但不代表免除費用。</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>https://www.ctbcbank.com/twrbo/zh_tw/cc_index/cc_product/cc_introduction_index/C_uniopen.html</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>海外,旅遊,點數回饋,加碼,期間限定</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>交叉來源：https://www.cardu.com.tw/message/detail.php?63682。</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>中國信託uniopen聯名卡統一企業集團指定品牌週期優惠</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>ctbc-uniopen-brand-weekly-promos-2026h2</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>dining</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2026/7/1至12/31，星巴克、foodomo、COLD STONE、博客來等統一企業集團品牌依指定日享優惠。</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>固定在統一企業集團指定品牌消費，願意依星期、門檻或App領券參加活動的持卡人。</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>星巴克每週一大杯飲料好友分享；COLD STONE指定日買1送1</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>foodomo週二滿NT$500贈50點；博客來週末滿NT$3,000最高加碼6%</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>活動期間依品牌公告，主要整理範圍為2026-07-01至2026-12-31。指定品牌與日期包含：星巴克週一購買兩杯大杯（含）以上飲料，其中一杯由星巴克招待；foodomo週二單筆滿NT$500贈OPENPOINT 50點，每月限量1,000名；COLD STONE週二及週五指定冰品買1送1；Yahoo購物中心／Yahoo拍賣週五累積滿NT$2,000且完成登錄享OPENPOINT 5%，每週上限200點、限量100名；博客來App週六日單筆滿NT$3,000最高加碼6%。夢時代與其他品牌優惠可能需於中國信託App領券，且各有名額、上限、指定商品或不可併用限制。</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>指定品牌買1送1／點數最高6%／滿額贈50點</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>各品牌依活動不同：foodomo每月限量1,000名；Yahoo每週上限200點且限量100名；博客來每戶每月上限200點；其他品牌依各自公告。</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>foodomo單筆滿NT$500；Yahoo累積滿NT$2,000；博客來單筆滿NT$3,000。</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>優惠依星期、品牌、支付方式及活動公告辦理；部分活動需於中信App領券或至平台登錄；名額額滿、商品售完、退貨或不適用支付方式均可能失去資格；不可與其他優惠合併者依品牌規則。</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>https://www.icashpay.com.tw/advertMessage/view/id/2370</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>指定通路,餐飲美食,點數回饋,需登錄,期間限定</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>官方交叉來源：https://www.ctbcbank.com/twrbo/zh_tw/cc_index/cc_product/cc_introduction_index/C_uniopen.html；https://www.cardu.com.tw/message/detail.php?63682；品牌細節以中信及各品牌最新公告為準。</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>中國信託華航聯名卡2026下半年哩程回饋</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>ctbc-china-airlines-mileage-rewards-2026h2</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>travel</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2026/7/1至12/31，三種卡等依消費類型累積華航哩程，生日月海外實體消費最高NT$6=1哩。</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>主要搭乘華航／華信航空，且可依卡等選擇哩程累積速度與年費的持卡人。</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>一般消費：鼎尊18元／哩、璀璨20元／哩、商務30元／哩</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>指定通路2倍；生日月海外實體3倍，鼎尊最優6元／哩</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>活動期間2026-07-01至2026-12-31。中國信託中華航空聯名卡依卡等累積華航哩程：鼎尊無限卡一般消費每NT$18=1哩、璀璨無限卡每NT$20=1哩、商務御璽卡每NT$30=1哩。國外實體商店、華航／華信航空官網機票、華航eMall、華航Sky Boutique、機上免稅品及指定訂房平台等享加碼2倍；生日當月國外實體商店享3倍，鼎尊無限卡最優NT$6=1哩。</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>點數回饋</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>最高NT$6=1哩</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>每月加碼哩程上限：鼎尊正卡80,000哩／附卡20,000哩；璀璨正卡60,000哩／附卡20,000哩；商務及各卡等附卡20,000哩。</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>依卡等與消費類型累積；生日月海外實體為生日當月消費。</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>須持有適用卡等；海外實體須為非台灣國別碼且面對面交易，Apple Pay、Google Pay、Samsung Pay於實體店可列入；網路交易、條碼支付、第三方支付及銀行不回饋交易不列入。指定訂房平台加碼限鼎尊／璀璨無限卡且須由帳單列示國外交易手續費。</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>https://www.ctbcbank.com/content/dam/minisite/long/creditcard/CTBCCI/index.html</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>旅遊,海外,點數回饋,加碼,期間限定,航空哩程</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>官方來源：https://www.ctbcbank.com/content/dam/minisite/long/creditcard/CTBCCI/index.html；卡優文章作為卡等比較與使用情境交叉整理。</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>中國信託華航聯名卡新戶迎賓與首刷哩程</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>ctbc-china-airlines-welcome-first-spend-2026h2</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>travel</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2026/7/1至12/31申請，依卡等完成綁定與首刷，最高可獲20,000哩。</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>首次申辦適用卡等，能在核卡後指定天數內完成一般消費並綁定華夏會員者。</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>鼎尊迎賓3,000哩＋核卡30天滿NT$8,888再贈17,000哩</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>璀璨迎賓2,000哩＋核卡30天滿NT$2,688再贈4,000哩；商務新戶滿NT$888贈1,000哩</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>申請收件日限2026-07-01至2026-12-31，且核准日須於2027-01-15前。鼎尊無限卡首次申辦綁定華夏會員並完成首刷享3,000哩，核卡30天內一般消費滿NT$8,888且繳交年費NT$22,000再享17,000哩；璀璨無限卡迎賓2,000哩，核卡30天內消費滿NT$2,688且繳年費NT$8,000再享4,000哩；商務御璽卡新戶核卡30天內消費滿NT$888享1,000哩。</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>點數回饋</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>最高20,000哩</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>迎賓禮限量30,000名；每戶正附卡合併限領一次；鼎尊／璀璨需繳交年費入帳。</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>鼎尊核卡30天一般消費滿NT$8,888；璀璨滿NT$2,688；商務滿NT$888。</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>新戶定義依卡等不同：鼎尊／璀璨為申辦前12個月未曾申辦任一中華航空聯名卡；商務為申辦前12個月未持有任何中信正卡（不含簽帳金融卡）。不含預借現金、基金申購、退貨、帳單分期、學費、繳稅、年費、手續費、利息及違約金等；首刷贈禮每戶限一次。</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>https://www.ctbcbank.com/content/dam/minisite/long/creditcard/CTBCCI/index.html</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>新戶,首刷,點數回饋,航空哩程,期間限定</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>官方來源：https://www.ctbcbank.com/content/dam/minisite/long/creditcard/CTBCCI/index.html；卡優文章補充三卡等迎賓與首刷比較。</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>中國信託華航聯名卡華夏金卡與機場尊榮禮遇</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>ctbc-china-airlines-elite-airport-benefits-2026h2</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>travel</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>鼎尊／璀璨首次申辦綁定華夏會員並完成首刷，最優享華夏金卡會籍2年／1年及機場禮遇。</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>搭乘華航頻率高，重視優先報到、優先登機、貴賓室、機場接送與額外行李者。</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>鼎尊首次申辦綁定華夏會員且首刷，享金卡會籍2年</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>璀璨同條件享金卡會籍1年；鼎尊／璀璨另有華航貴賓室與機場接送次數</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>活動期間2026-07-01至2026-12-31。首次申辦鼎尊無限卡或璀璨無限卡，完成中華航空華夏會員綁定與首刷後，鼎尊最優享華夏金卡會籍2年、璀璨享1年。華夏金卡可享快速訂位、優先候補、機場專屬櫃檯、額外免費托運行李、優先裝卸行李及全球機場貴賓室等禮遇；鼎尊與璀璨並提供中華航空貴賓室及國際機場接送服務，次數依卡等公告。</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>華夏金卡會籍2年／1年；貴賓室與機場接送</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>鼎尊與璀璨的貴賓室、接送次數依卡等；每人金卡升等禮遇限一次。</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>完成華夏會員綁定與首刷；部分禮遇需於中信官網或行動銀行提出升等申請。</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>僅鼎尊與璀璨適用華夏金卡升等；商務御璽卡不適用。申請人原已為華夏金卡、翡翠卡或晶鑽卡者不再升等或延續效期；註銷卡片可能取消會籍。相關使用規範以中信與中華航空公告為準。</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>https://www.ctbcbank.com/content/dam/minisite/long/creditcard/CTBCCI/index.html</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>旅遊,航空哩程,機場貴賓室,機場接送,期間限定</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>官方來源：https://www.ctbcbank.com/content/dam/minisite/long/creditcard/CTBCCI/index.html；卡優文章補充三卡等機場禮遇比較。</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>中國信託華航聯名卡機票折扣與哩程兌換</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>ctbc-china-airlines-award-tickets-flight-discount-2026h2</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>travel</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>華航官網購票享依卡等機票優惠，華航酬賓機票9,000哩起可兌換香港單程經濟艙。</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>會搭乘華航／華信，願意累積OPENPOINT以外的華航哩程並使用酬賓機票者。</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>華航酬賓機票：台灣至香港經濟艙單程9,000哩起</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>華航官網國際航線機票依卡等最優86折起；哩程兌換涵蓋亞洲、澳洲、紐澳、北美與歐洲航線</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>活動期間2026-07-01至2026-12-31。持中國信託中華航空聯名卡於華航官網指定網頁購買國際航線機票，依卡等享機票優惠，卡優整理為最優86折起。華航酬賓機票可由9,000哩兌換台灣至香港經濟艙單程，香港來回18,000哩；亞洲線、紐澳、北美與歐洲依航線及艙等需要不同哩程。酬賓機票須綁定華夏會員並透過華航網站兌換，機位、稅費、燃油費與退改票規則另依華航公告。</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>折扣</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>機票86折起；9,000哩起兌換</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>酬賓機位依當時空位；退票手續費NT$1,500或等值當地貨幣；稅款與附加費由持票人負擔。</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>至少9,000哩兌換台灣至香港經濟艙單程；需綁定華夏會員並於起飛前依規定線上兌換。</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>機票折扣依卡等、航線、艙等與華航指定頁面而定；哩程不得兌換現金，效期與兌換規定依華航華夏酬賓計畫；未使用或改票、未登機可能產生費用。</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>https://www.ctbcbank.com/content/dam/minisite/long/creditcard/CTBCCI/index.html</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>旅遊,航空哩程,機票,折扣,期間限定</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>官方來源：https://www.ctbcbank.com/content/dam/minisite/long/creditcard/CTBCCI/index.html；卡優文章補充機票折扣與兌換門檻。</t>
         </is>
       </c>
     </row>
@@ -3472,7 +6007,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33.38000106811523" customWidth="1" min="1" max="1"/>
@@ -3809,6 +6344,306 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>ctbc-linepay-rewards-2026h2</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>ctbc-line-pay-card</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>ctbc-linepay-overseas-physical-weekly-2026q3</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>ctbc-line-pay-card</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>ctbc-linepay-new-card-gift-2026h2</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>ctbc-line-pay-card</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>ctbc-linepay-ipass-transit-2026</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>ctbc-line-pay-card</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>taishin-richart-category-rewards-2026h2</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>taishin-richart-card</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>dawho-mobile-payment-new-card-2026h2</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>dawho-cashback-card</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>ctbc-linepay-overseas-physical-2026q3</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>ctbc-line-pay-card</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>fubon-momo-shopping-2026h2</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>fubon-momo-card</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>hsbc-cashback-signature-2026q3</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>hsbc-cashback-signature</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>dbs-eco-card-rewards-2026</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>dbs-eco-card</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>ctbc-uniopen-core-rewards-2026h2</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>ctbc-uniopen-card</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>ctbc-uniopen-icashpay-stack-2026q3</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>ctbc-uniopen-card</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>ctbc-uniopen-overseas-physical-2026h2</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>ctbc-uniopen-card</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>ctbc-uniopen-brand-weekly-promos-2026h2</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>ctbc-uniopen-card</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>ctbc-china-airlines-mileage-rewards-2026h2</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>ctbc-china-airlines-infinite-card</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>ctbc-china-airlines-mileage-rewards-2026h2</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>ctbc-china-airlines-signature-card</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>ctbc-china-airlines-mileage-rewards-2026h2</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>ctbc-china-airlines-business-signature-card</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>ctbc-china-airlines-welcome-first-spend-2026h2</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>ctbc-china-airlines-infinite-card</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>ctbc-china-airlines-welcome-first-spend-2026h2</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>ctbc-china-airlines-signature-card</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>ctbc-china-airlines-welcome-first-spend-2026h2</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>ctbc-china-airlines-business-signature-card</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>ctbc-china-airlines-elite-airport-benefits-2026h2</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>ctbc-china-airlines-infinite-card</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>ctbc-china-airlines-elite-airport-benefits-2026h2</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>ctbc-china-airlines-signature-card</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>ctbc-china-airlines-award-tickets-flight-discount-2026h2</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>ctbc-china-airlines-infinite-card</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>ctbc-china-airlines-award-tickets-flight-discount-2026h2</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>ctbc-china-airlines-signature-card</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>ctbc-china-airlines-award-tickets-flight-discount-2026h2</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>ctbc-china-airlines-business-signature-card</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
